--- a/tame_output/ON/bt/strategyON_20240315.xlsx
+++ b/tame_output/ON/bt/strategyON_20240315.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-51.5%</t>
+          <t>-52.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>105.7%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,11 +969,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>465.7%</t>
+          <t>466.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-278.0%</t>
+          <t>-279.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1127,11 +1127,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-107.2%</t>
+          <t>-107.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,32 +1308,32 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-210.6%</t>
+          <t>-162.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-79.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-42.6%</t>
+          <t>-43.5%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-6.176326673795995</v>
+        <v>-6.455692059914174</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.6610262449828874</v>
+        <v>0.5492800905356154</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.933147618525256</v>
+        <v>-1.212513004643436</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.572024767699879</v>
+        <v>2.404405536028971</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-6.172635748839583</v>
+        <v>-6.452001134957762</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.6625026149654518</v>
+        <v>0.5507564605181803</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.933147618525256</v>
+        <v>-1.212513004643436</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.572024767699879</v>
+        <v>2.404405536028971</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-6.165420395967767</v>
+        <v>-6.444785782085947</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.6709019532328204</v>
+        <v>0.5591557987855489</v>
       </c>
       <c r="F1878" t="n">
-        <v>-0.8633693832348741</v>
+        <v>-1.142734769353054</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.61940490599275</v>
+        <v>2.451785674321843</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-6.114392549885941</v>
+        <v>-6.39375793600412</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.6957956461499872</v>
+        <v>0.5840494917027153</v>
       </c>
       <c r="F1879" t="n">
-        <v>-0.7881600449277731</v>
+        <v>-1.067525431045953</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.669013063461447</v>
+        <v>2.501393831790539</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.040922718218493</v>
+        <v>-6.320288104336672</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.7405552803103874</v>
+        <v>0.6288091258631159</v>
       </c>
       <c r="F1880" t="n">
-        <v>-0.7146902132603248</v>
+        <v>-0.9940555993785045</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.728466663955337</v>
+        <v>2.560847432284429</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-5.960550362754563</v>
+        <v>-6.239915748872742</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.7872594432434763</v>
+        <v>0.6755132887962043</v>
       </c>
       <c r="F1881" t="n">
-        <v>-0.6343178577963952</v>
+        <v>-0.9136832439145749</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.791245297981212</v>
+        <v>2.623626066310304</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-5.927618492941712</v>
+        <v>-6.206983879059892</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.7932130262670207</v>
+        <v>0.6814668718197487</v>
       </c>
       <c r="F1882" t="n">
-        <v>-0.6343178577963952</v>
+        <v>-0.9136832439145749</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.784026133079616</v>
+        <v>2.616406901408708</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-5.947783134491259</v>
+        <v>-6.227148520609439</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.7784749788732257</v>
+        <v>0.6667288244259537</v>
       </c>
       <c r="F1883" t="n">
-        <v>-0.6544824993459425</v>
+        <v>-0.9338478854641222</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.765255157375911</v>
+        <v>2.597635925705004</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-5.889116204469726</v>
+        <v>-6.168481590587906</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.803057540720395</v>
+        <v>0.6913113862731235</v>
       </c>
       <c r="F1884" t="n">
-        <v>-0.5695230309158048</v>
+        <v>-0.8488884170339845</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.81734662827255</v>
+        <v>2.649727396601643</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-5.826046972163386</v>
+        <v>-6.105412358281566</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.830978962272046</v>
+        <v>0.7192328078247741</v>
       </c>
       <c r="F1885" t="n">
-        <v>-0.5980365935980393</v>
+        <v>-0.877401979716219</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.802932219292324</v>
+        <v>2.635312987621417</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-5.774031458194574</v>
+        <v>-6.053396844312753</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.8557755035459715</v>
+        <v>0.7440293490986996</v>
       </c>
       <c r="F1886" t="n">
-        <v>-0.5980365935980393</v>
+        <v>-0.877401979716219</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.806922554978725</v>
+        <v>2.639303323307817</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-5.59846178927367</v>
+        <v>-5.877827175391849</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.9245281442155915</v>
+        <v>0.8127819897683195</v>
       </c>
       <c r="F1887" t="n">
-        <v>-0.5980365935980393</v>
+        <v>-0.877401979716219</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.805447328079984</v>
+        <v>2.637828096409076</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-5.401192383545672</v>
+        <v>-5.680557769663851</v>
       </c>
       <c r="E1888" t="n">
-        <v>1.018489316671663</v>
+        <v>0.9067431622243913</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.4007671878700412</v>
+        <v>-0.6801325739882209</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.938862381681655</v>
+        <v>2.771243150010747</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-5.202040276308573</v>
+        <v>-5.481405662426752</v>
       </c>
       <c r="E1889" t="n">
-        <v>1.08509902591982</v>
+        <v>0.9733528714725477</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.2354446619202278</v>
+        <v>-0.5148100480384076</v>
       </c>
       <c r="G1889" t="n">
-        <v>3.025004763604859</v>
+        <v>2.857385531933952</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-4.976195123589162</v>
+        <v>-5.255560509707341</v>
       </c>
       <c r="E1890" t="n">
-        <v>1.185016160043793</v>
+        <v>1.073270005596521</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.1935179863330642</v>
+        <v>-0.4728833724512439</v>
       </c>
       <c r="G1890" t="n">
-        <v>3.059739841993367</v>
+        <v>2.892120610322459</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-4.689920311266468</v>
+        <v>-4.969285697384647</v>
       </c>
       <c r="E1891" t="n">
-        <v>1.300665229528929</v>
+        <v>1.188919075081657</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.1935179863330642</v>
+        <v>-0.4728833724512439</v>
       </c>
       <c r="G1891" t="n">
-        <v>3.060878986549425</v>
+        <v>2.893259754878517</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-4.463124484193134</v>
+        <v>-4.742489870311314</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.39401733452037</v>
+        <v>1.282271180073098</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.1254040417115196</v>
+        <v>-0.4047694278296994</v>
       </c>
       <c r="G1892" t="n">
-        <v>3.104381127484459</v>
+        <v>2.936761895813552</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-4.179215753264385</v>
+        <v>-4.458581139382565</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.513314531130506</v>
+        <v>1.401568376683235</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.1254040417115196</v>
+        <v>-0.4047694278296994</v>
       </c>
       <c r="G1893" t="n">
-        <v>3.110114831723096</v>
+        <v>2.942495600052188</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-3.932228503071433</v>
+        <v>-4.211593889189612</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.602372168813822</v>
+        <v>1.49062601436655</v>
       </c>
       <c r="F1894" t="n">
-        <v>0.1215832084814324</v>
+        <v>-0.1577821776367473</v>
       </c>
       <c r="G1894" t="n">
-        <v>3.248569919445002</v>
+        <v>3.080950687774094</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-3.668391635867364</v>
+        <v>-3.947757021985543</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.698023434382542</v>
+        <v>1.58627727993527</v>
       </c>
       <c r="F1895" t="n">
-        <v>0.1215832084814324</v>
+        <v>-0.1577821776367473</v>
       </c>
       <c r="G1895" t="n">
-        <v>3.238686438132095</v>
+        <v>3.071067206461187</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-3.401149834998967</v>
+        <v>-3.680515221117147</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.803085594230527</v>
+        <v>1.691339439783255</v>
       </c>
       <c r="F1896" t="n">
-        <v>0.1215832084814324</v>
+        <v>-0.1577821776367473</v>
       </c>
       <c r="G1896" t="n">
-        <v>3.236851877632721</v>
+        <v>3.069232645961813</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-3.125340671598483</v>
+        <v>-3.404706057716663</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.91310894461726</v>
+        <v>1.801362790169988</v>
       </c>
       <c r="F1897" t="n">
-        <v>0.2106025167601659</v>
+        <v>-0.06876286935801379</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.2899631476265</v>
+        <v>3.122343915955592</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-2.856273083831504</v>
+        <v>-3.135638469949683</v>
       </c>
       <c r="E1898" t="n">
-        <v>2.021404485869545</v>
+        <v>1.909658331422273</v>
       </c>
       <c r="F1898" t="n">
-        <v>0.4796701045271453</v>
+        <v>0.2003047184089656</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.452072206432181</v>
+        <v>3.284452974761273</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-2.592213145508707</v>
+        <v>-2.871578531626887</v>
       </c>
       <c r="E1899" t="n">
-        <v>2.113768145036912</v>
+        <v>2.00202199058964</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.7437300428499415</v>
+        <v>0.4643646567317617</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.597247853264107</v>
+        <v>3.429628621593199</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-1.88513352200387</v>
+        <v>-2.164498908122049</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.393812960778546</v>
+        <v>2.282066806331274</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.7437300428499415</v>
+        <v>0.4643646567317617</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.594460819603806</v>
+        <v>3.426841587932898</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-1.635492492017918</v>
+        <v>-1.914857878136097</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.494012996660768</v>
+        <v>2.382266842213496</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.9933710728358931</v>
+        <v>0.7140056867177135</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.744589061483218</v>
+        <v>3.57696982981231</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-1.380950592676842</v>
+        <v>-1.660315978795022</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.595196577617955</v>
+        <v>2.483450423170683</v>
       </c>
       <c r="F1902" t="n">
-        <v>1.247912972176969</v>
+        <v>0.968547586058789</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.896681022308621</v>
+        <v>3.729061790637713</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.564252589030635</v>
+        <v>3.567584098898368</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.164171879873678</v>
+        <v>-1.18020075910925</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.689832491577073</v>
+        <v>2.683420939882844</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.464691684980133</v>
+        <v>1.448662805744561</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.034672678828372</v>
+        <v>4.025055351287028</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240315.xlsx
+++ b/tame_output/ON/bt/strategyON_20240315.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-54.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>-46.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>466.1%</t>
+          <t>465.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-279.6%</t>
+          <t>-304.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-107.9%</t>
+          <t>-117.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,22 +1318,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-103.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-43.5%</t>
+          <t>-58.3%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.18020075910925</v>
+        <v>-1.426834756565423</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.683420939882844</v>
+        <v>2.584767340900375</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.448662805744561</v>
+        <v>1.202028808288388</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.025055351287028</v>
+        <v>3.877074952813325</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240315.xlsx
+++ b/tame_output/ON/bt/strategyON_20240315.xlsx
@@ -605,21 +605,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-15.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-54.4%</t>
+          <t>-54.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-46.6%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>465.2%</t>
+          <t>465.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-58.3%</t>
+          <t>-150.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1903"/>
+  <dimension ref="A1:G1904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.567584098898368</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45330,6 +45330,29 @@
       </c>
       <c r="G1903" t="n">
         <v>3.877074952813325</v>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="2" t="n">
+        <v>45366</v>
+      </c>
+      <c r="B1904" t="n">
+        <v>3.551340871700654</v>
+      </c>
+      <c r="C1904" t="n">
+        <v>2.960190827329692</v>
+      </c>
+      <c r="D1904" t="n">
+        <v>-1.426834756565423</v>
+      </c>
+      <c r="E1904" t="n">
+        <v>2.584767340900375</v>
+      </c>
+      <c r="F1904" t="n">
+        <v>1.202028808288388</v>
+      </c>
+      <c r="G1904" t="n">
+        <v>2.95325462431606</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240315.xlsx
+++ b/tame_output/ON/bt/strategyON_20240315.xlsx
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>

--- a/tame_output/ON/bt/strategyON_20240315.xlsx
+++ b/tame_output/ON/bt/strategyON_20240315.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>59.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-54.3%</t>
+          <t>-54.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-45.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>465.0%</t>
+          <t>468.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-304.3%</t>
+          <t>-304.8%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-117.7%</t>
+          <t>-118.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-162.6%</t>
+          <t>-161.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-103.8%</t>
+          <t>-104.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,42 +1466,42 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-150.7%</t>
+          <t>-58.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1904"/>
+  <dimension ref="A1:G1903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.872821101573119</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-6.455692059914174</v>
+        <v>-6.460896061015688</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.5492800905356154</v>
+        <v>0.5471984900950098</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.212513004643436</v>
+        <v>-1.217717005744949</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.404405536028971</v>
+        <v>2.401283135368063</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.595119541639607</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-6.452001134957762</v>
+        <v>-6.457205136059277</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.5507564605181803</v>
+        <v>0.5486748600775742</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.212513004643436</v>
+        <v>-1.217717005744949</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.404405536028971</v>
+        <v>2.401283135368063</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.60546122884381</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-6.444785782085947</v>
+        <v>-6.449989783187461</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.5591557987855489</v>
+        <v>0.5570741983449432</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142734769353054</v>
+        <v>-1.147938770454568</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.451785674321843</v>
+        <v>2.448663273660935</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.599522734431999</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-6.39375793600412</v>
+        <v>-6.398961937105635</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.5840494917027153</v>
+        <v>0.5819678912621096</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.067525431045953</v>
+        <v>-1.072729432147467</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.501393831790539</v>
+        <v>2.498271431129631</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.602642569142742</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.320288104336672</v>
+        <v>-6.325492105438187</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.6288091258631159</v>
+        <v>0.6267275254225098</v>
       </c>
       <c r="F1880" t="n">
-        <v>-0.9940555993785045</v>
+        <v>-0.9992596004800181</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.560847432284429</v>
+        <v>2.557725031623522</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.592730071310709</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-6.239915748872742</v>
+        <v>-6.245119749974257</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.6755132887962043</v>
+        <v>0.6734316883555986</v>
       </c>
       <c r="F1881" t="n">
-        <v>-0.9136832439145749</v>
+        <v>-0.9188872450160884</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.623626066310304</v>
+        <v>2.620503665649396</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.588549424112381</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-6.206983879059892</v>
+        <v>-6.212187880161406</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.6814668718197487</v>
+        <v>0.6793852713791431</v>
       </c>
       <c r="F1882" t="n">
-        <v>-0.9136832439145749</v>
+        <v>-0.9188872450160884</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.616406901408708</v>
+        <v>2.6132845007478</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.583363322466506</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-6.227148520609439</v>
+        <v>-6.232352521710953</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.6667288244259537</v>
+        <v>0.664647223985348</v>
       </c>
       <c r="F1883" t="n">
-        <v>-0.9338478854641222</v>
+        <v>-0.9390518865656358</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.597635925705004</v>
+        <v>2.594513525044095</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.596386844092696</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-6.168481590587906</v>
+        <v>-6.17368559168942</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.6913113862731235</v>
+        <v>0.6892297858325174</v>
       </c>
       <c r="F1884" t="n">
-        <v>-0.8488884170339845</v>
+        <v>-0.8540924181354981</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.649727396601643</v>
+        <v>2.646604995940734</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.594772470999509</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-6.105412358281566</v>
+        <v>-6.11061635938308</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.7192328078247741</v>
+        <v>0.7171512073841684</v>
       </c>
       <c r="F1885" t="n">
-        <v>-0.877401979716219</v>
+        <v>-0.8826059808177326</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.635312987621417</v>
+        <v>2.632190586960508</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.676344855024653</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-6.053396844312753</v>
+        <v>-6.058600845414268</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.7440293490986996</v>
+        <v>0.7419477486580939</v>
       </c>
       <c r="F1886" t="n">
-        <v>-0.877401979716219</v>
+        <v>-0.8826059808177326</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.639303323307817</v>
+        <v>2.636180922646909</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.702709094861031</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-5.877827175391849</v>
+        <v>-5.883031176493364</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.8127819897683195</v>
+        <v>0.8107003893277138</v>
       </c>
       <c r="F1887" t="n">
-        <v>-0.877401979716219</v>
+        <v>-0.8826059808177326</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.637828096409076</v>
+        <v>2.634705695748167</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.794242563642827</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-5.680557769663851</v>
+        <v>-5.685761770765366</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.9067431622243913</v>
+        <v>0.9046615617837857</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.6801325739882209</v>
+        <v>-0.6853365750897344</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.771243150010747</v>
+        <v>2.768120749349839</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.779512379472687</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-5.481405662426752</v>
+        <v>-5.486609663528267</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.9733528714725477</v>
+        <v>0.971271271031942</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.5148100480384076</v>
+        <v>-0.5200140491399211</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.857385531933952</v>
+        <v>2.854263131273044</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.78783221131739</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-5.255560509707341</v>
+        <v>-5.260764510808856</v>
       </c>
       <c r="E1890" t="n">
-        <v>1.073270005596521</v>
+        <v>1.071188405155915</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.4728833724512439</v>
+        <v>-0.4780873735527574</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.892120610322459</v>
+        <v>2.88899820966155</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.787514653514212</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-4.969285697384647</v>
+        <v>-4.974489698486162</v>
       </c>
       <c r="E1891" t="n">
-        <v>1.188919075081657</v>
+        <v>1.186837474641052</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.4728833724512439</v>
+        <v>-0.4780873735527574</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.893259754878517</v>
+        <v>2.890137354217609</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.813606363348327</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-4.742489870311314</v>
+        <v>-4.747693871412828</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.282271180073098</v>
+        <v>1.280189579632493</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.4047694278296994</v>
+        <v>-0.4099734289312129</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.936761895813552</v>
+        <v>2.933639495152644</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.871622504313679</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-4.458581139382565</v>
+        <v>-4.463785140484079</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.401568376683235</v>
+        <v>1.399486776242629</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.4047694278296994</v>
+        <v>-0.4099734289312129</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.942495600052188</v>
+        <v>2.93937319939128</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.83124875965744</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-4.211593889189612</v>
+        <v>-4.216797890291127</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.49062601436655</v>
+        <v>1.488544413925944</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.1577821776367473</v>
+        <v>-0.1629861787382608</v>
       </c>
       <c r="G1894" t="n">
-        <v>3.080950687774094</v>
+        <v>3.077828287113186</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.850373489934524</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-3.947757021985543</v>
+        <v>-3.952961023087058</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.58627727993527</v>
+        <v>1.584195679494665</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.1577821776367473</v>
+        <v>-0.1629861787382608</v>
       </c>
       <c r="G1895" t="n">
-        <v>3.071067206461187</v>
+        <v>3.067944805800279</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.86898790913834</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-3.680515221117147</v>
+        <v>-3.685719222218661</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.691339439783255</v>
+        <v>1.68925783934265</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.1577821776367473</v>
+        <v>-0.1629861787382608</v>
       </c>
       <c r="G1896" t="n">
-        <v>3.069232645961813</v>
+        <v>3.066110245300905</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.887355351014062</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-3.404706057716663</v>
+        <v>-3.409910058818177</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.801362790169988</v>
+        <v>1.799281189729382</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.06876286935801379</v>
+        <v>-0.07396687045952732</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.122343915955592</v>
+        <v>3.119221515294684</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.903500183799357</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-3.135638469949683</v>
+        <v>-3.140842471051198</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.909658331422273</v>
+        <v>1.907576730981668</v>
       </c>
       <c r="F1898" t="n">
-        <v>0.2003047184089656</v>
+        <v>0.195100717307452</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.284452974761273</v>
+        <v>3.281330574100366</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.891981941719886</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-2.871578531626887</v>
+        <v>-2.876782532728401</v>
       </c>
       <c r="E1899" t="n">
-        <v>2.00202199058964</v>
+        <v>1.999940390149034</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.4643646567317617</v>
+        <v>0.4591606556302482</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.429628621593199</v>
+        <v>3.426506220932291</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.935923577541841</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-2.164498908122049</v>
+        <v>-2.169702909223564</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.282066806331274</v>
+        <v>2.279985205890668</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.4643646567317617</v>
+        <v>0.4591606556302482</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.426841587932898</v>
+        <v>3.42371918727199</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.942045277090843</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-1.914857878136097</v>
+        <v>-1.920061879237612</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.382266842213496</v>
+        <v>2.380185241772891</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.7140056867177135</v>
+        <v>0.7088016856161999</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.57696982981231</v>
+        <v>3.573847429151403</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.958832581328588</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-1.660315978795022</v>
+        <v>-1.665519979896536</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.483450423170683</v>
+        <v>2.481368822730078</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.968547586058789</v>
+        <v>0.9633435849572755</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.729061790637713</v>
+        <v>3.725939389976805</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,45 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.879290309410559</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.426834756565423</v>
+        <v>-1.432038757666938</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.584767340900375</v>
+        <v>2.582685740459769</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.202028808288388</v>
+        <v>1.196824807186874</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.877074952813325</v>
-      </c>
-    </row>
-    <row r="1904">
-      <c r="A1904" s="2" t="n">
-        <v>45366</v>
-      </c>
-      <c r="B1904" t="n">
-        <v>3.551340871700654</v>
-      </c>
-      <c r="C1904" t="n">
-        <v>2.960190827329692</v>
-      </c>
-      <c r="D1904" t="n">
-        <v>-1.426834756565423</v>
-      </c>
-      <c r="E1904" t="n">
-        <v>2.584767340900375</v>
-      </c>
-      <c r="F1904" t="n">
-        <v>1.202028808288388</v>
-      </c>
-      <c r="G1904" t="n">
-        <v>2.95325462431606</v>
+        <v>3.873952552152416</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240315.xlsx
+++ b/tame_output/ON/bt/strategyON_20240315.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-54.4%</t>
+          <t>-53.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,15 +969,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-361.3%</t>
+          <t>-392.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-45.4%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>468.0%</t>
+          <t>469.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-304.8%</t>
+          <t>-289.5%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1127,15 +1127,15 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-144.9%</t>
+          <t>-157.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-118.0%</t>
+          <t>-112.1%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,47 +1308,47 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.8%</t>
+          <t>-210.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-104.3%</t>
+          <t>-69.6%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-58.6%</t>
+          <t>-38.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1903"/>
+  <dimension ref="A1:G1904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43641,10 +43641,10 @@
         <v>3.127238527942291</v>
       </c>
       <c r="D1830" t="n">
-        <v>1.578971084556756</v>
+        <v>1.26606255345954</v>
       </c>
       <c r="E1830" t="n">
-        <v>3.758470537451246</v>
+        <v>3.633307125012359</v>
       </c>
       <c r="F1830" t="n">
         <v>2.239927473767815</v>
@@ -43658,16 +43658,16 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612274</v>
+        <v>3.346417924612275</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
       </c>
       <c r="D1831" t="n">
-        <v>1.559919339547285</v>
+        <v>1.24701080845007</v>
       </c>
       <c r="E1831" t="n">
-        <v>3.751214584972977</v>
+        <v>3.62605117253409</v>
       </c>
       <c r="F1831" t="n">
         <v>2.220875728758345</v>
@@ -43687,10 +43687,10 @@
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>1.555319320002939</v>
+        <v>1.242410788905723</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.751840582777937</v>
+        <v>3.62667717033905</v>
       </c>
       <c r="F1832" t="n">
         <v>2.216275709213999</v>
@@ -43710,10 +43710,10 @@
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>1.50748095775674</v>
+        <v>1.194572426659524</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.729577291781169</v>
+        <v>3.604413879342283</v>
       </c>
       <c r="F1833" t="n">
         <v>2.216275709213999</v>
@@ -43733,10 +43733,10 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>1.436132850517166</v>
+        <v>1.12322431941995</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.714014658168729</v>
+        <v>3.588851245729843</v>
       </c>
       <c r="F1834" t="n">
         <v>2.144927601974425</v>
@@ -43756,10 +43756,10 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>1.435581050675354</v>
+        <v>1.122672519578138</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.712051774094349</v>
+        <v>3.586888361655462</v>
       </c>
       <c r="F1835" t="n">
         <v>2.145769365459731</v>
@@ -43779,10 +43779,10 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>1.329894162733054</v>
+        <v>1.016985631635838</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.649602291544876</v>
+        <v>3.52443887910599</v>
       </c>
       <c r="F1836" t="n">
         <v>2.131208291757047</v>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>1.335743543848299</v>
+        <v>1.022835012751082</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.652431182716848</v>
+        <v>3.527267770277962</v>
       </c>
       <c r="F1837" t="n">
         <v>2.131208291757047</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>1.287521277001215</v>
+        <v>0.9746127459039988</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.637222258599682</v>
+        <v>3.512058846160795</v>
       </c>
       <c r="F1838" t="n">
         <v>2.082986024909964</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>1.295356538838099</v>
+        <v>0.9824480077408831</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.675297447831977</v>
+        <v>3.55013403539309</v>
       </c>
       <c r="F1839" t="n">
         <v>2.082986024909964</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>1.300394129565686</v>
+        <v>0.9874855984684696</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.67588992430835</v>
+        <v>3.550726511869463</v>
       </c>
       <c r="F1840" t="n">
         <v>2.138630481176281</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>1.243924498389389</v>
+        <v>0.9310159672921728</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.632048453461568</v>
+        <v>3.506885041022681</v>
       </c>
       <c r="F1841" t="n">
         <v>2.082160849999984</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>1.178157108339977</v>
+        <v>0.8652485772427607</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.606759106572273</v>
+        <v>3.481595694133387</v>
       </c>
       <c r="F1842" t="n">
         <v>2.082160849999984</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>1.164621624563267</v>
+        <v>0.8517130934660511</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.591972945049345</v>
+        <v>3.466809532610458</v>
       </c>
       <c r="F1843" t="n">
         <v>2.082160849999984</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>1.082849724135516</v>
+        <v>0.7699411930382993</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.549346910833482</v>
+        <v>3.424183498394596</v>
       </c>
       <c r="F1844" t="n">
         <v>2.109196423406121</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>1.015640616263638</v>
+        <v>0.7027320851664216</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.527228584518434</v>
+        <v>3.402065172079547</v>
       </c>
       <c r="F1845" t="n">
         <v>2.109196423406121</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>1.019632069058828</v>
+        <v>0.7067235379616118</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.52664996175575</v>
+        <v>3.401486549316864</v>
       </c>
       <c r="F1846" t="n">
         <v>2.113187876201311</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>0.8679350220148928</v>
+        <v>0.5550264909176768</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.463898034443239</v>
+        <v>3.338734622004353</v>
       </c>
       <c r="F1847" t="n">
         <v>1.961490829157376</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>0.6463130884567754</v>
+        <v>0.3334045573595593</v>
       </c>
       <c r="E1848" t="n">
-        <v>3.375115477618914</v>
+        <v>3.249952065180028</v>
       </c>
       <c r="F1848" t="n">
         <v>1.923964695470007</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>0.4383090301036981</v>
+        <v>0.125400499006482</v>
       </c>
       <c r="E1849" t="n">
-        <v>3.296805998831609</v>
+        <v>3.171642586392722</v>
       </c>
       <c r="F1849" t="n">
         <v>1.923964695470007</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>0.1679090673948128</v>
+        <v>-0.1449994637024033</v>
       </c>
       <c r="E1850" t="n">
-        <v>3.183727470086042</v>
+        <v>3.058564057647156</v>
       </c>
       <c r="F1850" t="n">
         <v>1.653564732761122</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>0.1612741448978827</v>
+        <v>-0.1516343861993334</v>
       </c>
       <c r="E1851" t="n">
-        <v>3.174157800393719</v>
+        <v>3.048994387954833</v>
       </c>
       <c r="F1851" t="n">
         <v>1.646929810264191</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-0.1667430768295965</v>
+        <v>-0.4796516079268126</v>
       </c>
       <c r="E1852" t="n">
-        <v>3.063289201441496</v>
+        <v>2.938125789002609</v>
       </c>
       <c r="F1852" t="n">
         <v>1.318912588536712</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-0.1634063303206248</v>
+        <v>-0.476314861417841</v>
       </c>
       <c r="E1853" t="n">
-        <v>3.072722650453653</v>
+        <v>2.947559238014767</v>
       </c>
       <c r="F1853" t="n">
         <v>1.321604620955744</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-0.5301173819871705</v>
+        <v>-0.8430259130843866</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.927144621830767</v>
+        <v>2.801981209391881</v>
       </c>
       <c r="F1854" t="n">
         <v>0.9548935692891981</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-0.5305480810357659</v>
+        <v>-0.8434566121329821</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.925514881024192</v>
+        <v>2.800351468585306</v>
       </c>
       <c r="F1855" t="n">
         <v>0.9548935692891981</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-0.8742308542624286</v>
+        <v>-1.187139385359645</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.789810895188143</v>
+        <v>2.664647482749257</v>
       </c>
       <c r="F1856" t="n">
         <v>0.8469875172619798</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-1.231881204500777</v>
+        <v>-1.544789735597993</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.642856813749062</v>
+        <v>2.517693401310175</v>
       </c>
       <c r="F1857" t="n">
         <v>0.4893371670236317</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-1.238542144722925</v>
+        <v>-1.551450675820141</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.641965364360462</v>
+        <v>2.516801951921576</v>
       </c>
       <c r="F1858" t="n">
         <v>0.4893371670236317</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-1.670347937872712</v>
+        <v>-1.983256468969929</v>
       </c>
       <c r="E1859" t="n">
-        <v>2.455575934567952</v>
+        <v>2.330412522129065</v>
       </c>
       <c r="F1859" t="n">
         <v>0.3529196705823647</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-1.996780466740456</v>
+        <v>-2.309688997837672</v>
       </c>
       <c r="E1860" t="n">
-        <v>2.313287698022945</v>
+        <v>2.188124285584058</v>
       </c>
       <c r="F1860" t="n">
         <v>0.2704514200752166</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-1.998344617850759</v>
+        <v>-2.311253148947976</v>
       </c>
       <c r="E1861" t="n">
-        <v>2.311242629234789</v>
+        <v>2.186079216795902</v>
       </c>
       <c r="F1861" t="n">
         <v>0.2704514200752166</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-2.361970862751072</v>
+        <v>-2.674879393848288</v>
       </c>
       <c r="E1862" t="n">
-        <v>2.172279691508905</v>
+        <v>2.047116279070019</v>
       </c>
       <c r="F1862" t="n">
         <v>0.1722297832080907</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-2.359543798222353</v>
+        <v>-2.67245232931957</v>
       </c>
       <c r="E1863" t="n">
-        <v>2.172505032326224</v>
+        <v>2.047341619887337</v>
       </c>
       <c r="F1863" t="n">
         <v>0.1718970014009391</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-2.768132575403032</v>
+        <v>-3.081041106500249</v>
       </c>
       <c r="E1864" t="n">
-        <v>2.007831065468712</v>
+        <v>1.882667653029825</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.2366917757797393</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-3.181115059544125</v>
+        <v>-3.494023590641342</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.837823504283735</v>
+        <v>1.712660091844848</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.2366917757797393</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-3.597506933831123</v>
+        <v>-3.910415464928339</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.669260805177813</v>
+        <v>1.544097392738927</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.2366917757797393</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-3.974183944360967</v>
+        <v>-4.287092475458183</v>
       </c>
       <c r="E1867" t="n">
-        <v>1.528848691634555</v>
+        <v>1.403685279195668</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.2366917757797393</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-3.987898808686078</v>
+        <v>-4.300807339783295</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.519462311050205</v>
+        <v>1.394298898611319</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.2366917757797393</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-4.300723607931058</v>
+        <v>-4.613632139028274</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.392737311407214</v>
+        <v>1.267573898968328</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.2366917757797393</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-4.305536646396395</v>
+        <v>-4.618445177493611</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.394591071950288</v>
+        <v>1.269427659511401</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.2382384104825251</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-4.738885754506631</v>
+        <v>-5.051794285603847</v>
       </c>
       <c r="E1871" t="n">
-        <v>1.21722512417179</v>
+        <v>1.092061711732903</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.2382384104825251</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-5.121887143249262</v>
+        <v>-5.434795674346478</v>
       </c>
       <c r="E1872" t="n">
-        <v>1.063922467353154</v>
+        <v>0.938759054914267</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.2382384104825251</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-5.49687246942054</v>
+        <v>-5.809781000517756</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.9164998528560728</v>
+        <v>0.7913364404171865</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.6132237366538026</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-5.856402791924541</v>
+        <v>-6.169311323021757</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.7780380271525225</v>
+        <v>0.6528746147136357</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.6132237366538026</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-6.182802820589554</v>
+        <v>-6.49571135168677</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.6553940356436945</v>
+        <v>0.5302306232048082</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.9396237653188155</v>
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.872821101573119</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-6.460896061015688</v>
+        <v>-6.489235204893211</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.5471984900950098</v>
+        <v>0.5358628325440007</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.217717005744949</v>
+        <v>-0.933147618525256</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.401283135368063</v>
+        <v>2.572024767699879</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.595119541639607</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-6.457205136059277</v>
+        <v>-6.485544279936799</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.5486748600775742</v>
+        <v>0.5373392025265655</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.217717005744949</v>
+        <v>-0.933147618525256</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.401283135368063</v>
+        <v>2.572024767699879</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.60546122884381</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-6.449989783187461</v>
+        <v>-6.478328927064983</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.5570741983449432</v>
+        <v>0.5457385407939341</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.147938770454568</v>
+        <v>-0.8633693832348741</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.448663273660935</v>
+        <v>2.61940490599275</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.599522734431999</v>
+        <v>3.496848329199884</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-6.398961937105635</v>
+        <v>-6.427301080983157</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.5819678912621096</v>
+        <v>0.5706322337111005</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.072729432147467</v>
+        <v>-0.7881600449277731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.498271431129631</v>
+        <v>2.669013063461447</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.602642569142742</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.325492105438187</v>
+        <v>-6.353831249315709</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.6267275254225098</v>
+        <v>0.6153918678715011</v>
       </c>
       <c r="F1880" t="n">
-        <v>-0.9992596004800181</v>
+        <v>-0.7146902132603248</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.557725031623522</v>
+        <v>2.728466663955337</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.592730071310709</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-6.245119749974257</v>
+        <v>-6.273458893851779</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.6734316883555986</v>
+        <v>0.66209603080459</v>
       </c>
       <c r="F1881" t="n">
-        <v>-0.9188872450160884</v>
+        <v>-0.6343178577963952</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.620503665649396</v>
+        <v>2.791245297981212</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.588549424112381</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-6.212187880161406</v>
+        <v>-6.240527024038928</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.6793852713791431</v>
+        <v>0.668049613828134</v>
       </c>
       <c r="F1882" t="n">
-        <v>-0.9188872450160884</v>
+        <v>-0.6343178577963952</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.6132845007478</v>
+        <v>2.784026133079616</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.583363322466506</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-6.232352521710953</v>
+        <v>-6.260691665588475</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.664647223985348</v>
+        <v>0.653311566434339</v>
       </c>
       <c r="F1883" t="n">
-        <v>-0.9390518865656358</v>
+        <v>-0.6544824993459425</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.594513525044095</v>
+        <v>2.765255157375911</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.596386844092696</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-6.17368559168942</v>
+        <v>-6.202024735566942</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.6892297858325174</v>
+        <v>0.6778941282815087</v>
       </c>
       <c r="F1884" t="n">
-        <v>-0.8540924181354981</v>
+        <v>-0.5695230309158048</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.646604995940734</v>
+        <v>2.81734662827255</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.594772470999509</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-6.11061635938308</v>
+        <v>-6.138955503260602</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.7171512073841684</v>
+        <v>0.7058155498331593</v>
       </c>
       <c r="F1885" t="n">
-        <v>-0.8826059808177326</v>
+        <v>-0.5980365935980393</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.632190586960508</v>
+        <v>2.802932219292324</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.676344855024653</v>
+        <v>3.573670449792538</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-6.058600845414268</v>
+        <v>-6.08693998929179</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.7419477486580939</v>
+        <v>0.7306120911070852</v>
       </c>
       <c r="F1886" t="n">
-        <v>-0.8826059808177326</v>
+        <v>-0.5980365935980393</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.636180922646909</v>
+        <v>2.806922554978725</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.702709094861031</v>
+        <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-5.883031176493364</v>
+        <v>-5.911370320370886</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.8107003893277138</v>
+        <v>0.7993647317767052</v>
       </c>
       <c r="F1887" t="n">
-        <v>-0.8826059808177326</v>
+        <v>-0.5980365935980393</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.634705695748167</v>
+        <v>2.805447328079984</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.794242563642827</v>
+        <v>3.691568158410712</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-5.685761770765366</v>
+        <v>-5.714100914642888</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.9046615617837857</v>
+        <v>0.8933259042327766</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.6853365750897344</v>
+        <v>-0.4007671878700412</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.768120749349839</v>
+        <v>2.938862381681655</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.779512379472687</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-5.486609663528267</v>
+        <v>-5.514948807405789</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.971271271031942</v>
+        <v>0.9599356134809334</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.5200140491399211</v>
+        <v>-0.2354446619202278</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.854263131273044</v>
+        <v>3.025004763604859</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.78783221131739</v>
+        <v>3.685157806085275</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-5.260764510808856</v>
+        <v>-5.289103654686378</v>
       </c>
       <c r="E1890" t="n">
-        <v>1.071188405155915</v>
+        <v>1.059852747604906</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.4780873735527574</v>
+        <v>-0.1935179863330642</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.88899820966155</v>
+        <v>3.059739841993367</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.787514653514212</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-4.974489698486162</v>
+        <v>-5.002828842363684</v>
       </c>
       <c r="E1891" t="n">
-        <v>1.186837474641052</v>
+        <v>1.175501817090043</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.4780873735527574</v>
+        <v>-0.1935179863330642</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.890137354217609</v>
+        <v>3.060878986549425</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.813606363348327</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-4.747693871412828</v>
+        <v>-4.77603301529035</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.280189579632493</v>
+        <v>1.268853922081484</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.4099734289312129</v>
+        <v>-0.1254040417115196</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.933639495152644</v>
+        <v>3.104381127484459</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.871622504313679</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-4.463785140484079</v>
+        <v>-4.492124284361601</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.399486776242629</v>
+        <v>1.38815111869162</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.4099734289312129</v>
+        <v>-0.1254040417115196</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.93937319939128</v>
+        <v>3.110114831723096</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.83124875965744</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-4.216797890291127</v>
+        <v>-4.245137034168649</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.488544413925944</v>
+        <v>1.477208756374936</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.1629861787382608</v>
+        <v>0.1215832084814324</v>
       </c>
       <c r="G1894" t="n">
-        <v>3.077828287113186</v>
+        <v>3.248569919445002</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.850373489934524</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-3.952961023087058</v>
+        <v>-3.98130016696458</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.584195679494665</v>
+        <v>1.572860021943656</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.1629861787382608</v>
+        <v>0.1215832084814324</v>
       </c>
       <c r="G1895" t="n">
-        <v>3.067944805800279</v>
+        <v>3.238686438132095</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.86898790913834</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-3.685719222218661</v>
+        <v>-3.714058366096183</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.68925783934265</v>
+        <v>1.677922181791641</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.1629861787382608</v>
+        <v>0.1215832084814324</v>
       </c>
       <c r="G1896" t="n">
-        <v>3.066110245300905</v>
+        <v>3.236851877632721</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.887355351014062</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-3.409910058818177</v>
+        <v>-3.438249202695699</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.799281189729382</v>
+        <v>1.787945532178373</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.07396687045952732</v>
+        <v>0.2106025167601659</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.119221515294684</v>
+        <v>3.2899631476265</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.903500183799357</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-3.140842471051198</v>
+        <v>-3.16918161492872</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.907576730981668</v>
+        <v>1.896241073430659</v>
       </c>
       <c r="F1898" t="n">
-        <v>0.195100717307452</v>
+        <v>0.4796701045271453</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.281330574100366</v>
+        <v>3.452072206432181</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.891981941719886</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-2.876782532728401</v>
+        <v>-2.905121676605924</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.999940390149034</v>
+        <v>1.988604732598025</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.4591606556302482</v>
+        <v>0.7437300428499415</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.426506220932291</v>
+        <v>3.597247853264107</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.935923577541841</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-2.169702909223564</v>
+        <v>-2.198042053101086</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.279985205890668</v>
+        <v>2.268649548339659</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.4591606556302482</v>
+        <v>0.7437300428499415</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.42371918727199</v>
+        <v>3.594460819603806</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.942045277090843</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-1.920061879237612</v>
+        <v>-1.948401023115134</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.380185241772891</v>
+        <v>2.368849584221882</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.7088016856161999</v>
+        <v>0.9933710728358931</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.573847429151403</v>
+        <v>3.744589061483218</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.958832581328588</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-1.665519979896536</v>
+        <v>-1.693859123774059</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.481368822730078</v>
+        <v>2.470033165179069</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.9633435849572755</v>
+        <v>1.247912972176969</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.725939389976805</v>
+        <v>3.896681022308621</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,45 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.879290309410559</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.432038757666938</v>
+        <v>-1.46037790154446</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.582685740459769</v>
+        <v>2.571350082908761</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.196824807186874</v>
+        <v>1.481394194406567</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.873952552152416</v>
+        <v>4.044694184484232</v>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="2" t="n">
+        <v>45366</v>
+      </c>
+      <c r="B1904" t="n">
+        <v>3.544283825361688</v>
+      </c>
+      <c r="C1904" t="n">
+        <v>3.152965457527332</v>
+      </c>
+      <c r="D1904" t="n">
+        <v>-1.279601660069634</v>
+      </c>
+      <c r="E1904" t="n">
+        <v>2.640768369185732</v>
+      </c>
+      <c r="F1904" t="n">
+        <v>1.543520930867389</v>
+      </c>
+      <c r="G1904" t="n">
+        <v>4.079078016047767</v>
       </c>
     </row>
   </sheetData>
